--- a/Excel/DefendBuffConfig.xlsx
+++ b/Excel/DefendBuffConfig.xlsx
@@ -1,10 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="28800" windowHeight="12375"/>
+    <workbookView windowHeight="17680"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -56,12 +56,84 @@
         </r>
       </text>
     </comment>
+    <comment ref="F3" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 属性
+2 词条
+3 技能</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="E4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 属性
+2 词条
+3 技能</t>
+        </r>
+      </text>
+    </comment>
+    <comment ref="F4" authorId="0">
+      <text>
+        <r>
+          <rPr>
+            <b/>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t>admin:</t>
+        </r>
+        <r>
+          <rPr>
+            <sz val="9"/>
+            <rFont val="宋体"/>
+            <charset val="134"/>
+          </rPr>
+          <t xml:space="preserve">
+1 属性
+2 词条
+3 技能</t>
+        </r>
+      </text>
+    </comment>
   </commentList>
 </comments>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="77" uniqueCount="42">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="106" uniqueCount="51">
   <si>
     <t>#</t>
   </si>
@@ -72,7 +144,10 @@
     <t>Name</t>
   </si>
   <si>
-    <t>Type</t>
+    <t>StartCycle</t>
+  </si>
+  <si>
+    <t>EndCycle</t>
   </si>
   <si>
     <t>MaxCount</t>
@@ -165,28 +240,52 @@
     <t>减伤(大)</t>
   </si>
   <si>
-    <t>多重雷电</t>
-  </si>
-  <si>
-    <t>雷电术施法目标+4</t>
-  </si>
-  <si>
-    <t>多重火符</t>
-  </si>
-  <si>
-    <t>火符术施法目标+1</t>
-  </si>
-  <si>
-    <t>分身术(20级)</t>
-  </si>
-  <si>
-    <t>创造一个分身</t>
-  </si>
-  <si>
-    <t>烈火剑法(追击)</t>
-  </si>
-  <si>
-    <t>每隔2s释放一次烈火剑法</t>
+    <t>提高{0}%攻击倍率</t>
+  </si>
+  <si>
+    <t>提高{0}%防御倍率</t>
+  </si>
+  <si>
+    <t>韧性(小)</t>
+  </si>
+  <si>
+    <t>提高{0}%韧性倍率</t>
+  </si>
+  <si>
+    <t>韧性(中)</t>
+  </si>
+  <si>
+    <t>韧性(大)</t>
+  </si>
+  <si>
+    <t>提高{0}%生命倍率</t>
+  </si>
+  <si>
+    <t>增加{0}%增伤倍率</t>
+  </si>
+  <si>
+    <t>命中(小)</t>
+  </si>
+  <si>
+    <t>增加{0}%命中</t>
+  </si>
+  <si>
+    <t>命中(中)</t>
+  </si>
+  <si>
+    <t>命中(大)</t>
+  </si>
+  <si>
+    <t>闪避(小)</t>
+  </si>
+  <si>
+    <t>增加{0}%闪避</t>
+  </si>
+  <si>
+    <t>闪避(中)</t>
+  </si>
+  <si>
+    <t>闪避(大)</t>
   </si>
 </sst>
 </file>
@@ -199,7 +298,7 @@
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
-  <fonts count="26">
+  <fonts count="25">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -223,12 +322,6 @@
       <sz val="9"/>
       <color theme="1"/>
       <name val="等线"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <color theme="1"/>
-      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
@@ -717,144 +810,143 @@
     <xf numFmtId="42" fontId="0" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="4" borderId="1" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="18" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="19" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="23" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="22" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="5" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="6" borderId="5" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="6" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="7" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="22" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1174,25 +1266,25 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A2:AB26"/>
+  <dimension ref="A2:AC42"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16" customHeight="1"/>
   <cols>
     <col min="1" max="3" width="9" style="2"/>
     <col min="4" max="4" width="12.25" style="2" customWidth="1"/>
-    <col min="5" max="6" width="11.875" style="2" customWidth="1"/>
-    <col min="7" max="7" width="10.875" style="2" customWidth="1"/>
-    <col min="8" max="10" width="13" style="2" customWidth="1"/>
-    <col min="11" max="12" width="19" style="2" customWidth="1"/>
-    <col min="13" max="13" width="14.25" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="5" max="7" width="11.875" style="2" customWidth="1"/>
+    <col min="8" max="8" width="10.875" style="2" customWidth="1"/>
+    <col min="9" max="11" width="13" style="2" customWidth="1"/>
+    <col min="12" max="13" width="19" style="2" customWidth="1"/>
+    <col min="14" max="14" width="14.25" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" customHeight="1" spans="13:13">
-      <c r="M2" s="2" t="s">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" customHeight="1" spans="3:13">
+    <row r="2" customHeight="1" spans="14:14">
+      <c r="N2" s="2" t="s">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" customHeight="1" spans="3:14">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1223,11 +1315,14 @@
       <c r="L3" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M3" s="3"/>
-    </row>
-    <row r="4" customHeight="1" spans="3:13">
+      <c r="M3" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N3" s="3"/>
+    </row>
+    <row r="4" customHeight="1" spans="3:14">
       <c r="C4" s="3" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="D4" s="3" t="s">
         <v>2</v>
@@ -1256,107 +1351,118 @@
       <c r="L4" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="M4" s="3"/>
-    </row>
-    <row r="5" customHeight="1" spans="3:13">
+      <c r="M4" s="3" t="s">
+        <v>11</v>
+      </c>
+      <c r="N4" s="3"/>
+    </row>
+    <row r="5" customHeight="1" spans="3:14">
       <c r="C5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="D5" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="E5" s="3" t="s">
         <v>13</v>
       </c>
-      <c r="E5" s="3" t="s">
-        <v>12</v>
-      </c>
       <c r="F5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="G5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="H5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="I5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="J5" s="3" t="s">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="K5" s="3" t="s">
         <v>13</v>
       </c>
       <c r="L5" s="3" t="s">
-        <v>12</v>
-      </c>
-      <c r="M5" s="3"/>
-    </row>
-    <row r="6" customHeight="1" spans="3:12">
+        <v>14</v>
+      </c>
+      <c r="M5" s="3" t="s">
+        <v>13</v>
+      </c>
+      <c r="N5" s="3"/>
+    </row>
+    <row r="6" customHeight="1" spans="3:13">
       <c r="C6" s="2">
         <v>1</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="E6" s="2">
         <v>1</v>
       </c>
       <c r="F6" s="2">
+        <v>6</v>
+      </c>
+      <c r="G6" s="2">
         <v>4</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>2001</v>
       </c>
-      <c r="H6" s="2">
-        <v>10</v>
-      </c>
       <c r="I6" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J6" s="2">
         <v>0</v>
       </c>
-      <c r="K6" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L6" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:28">
+      <c r="K6" s="2">
+        <v>0</v>
+      </c>
+      <c r="L6" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M6" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="7" s="1" customFormat="1" customHeight="1" spans="1:29">
       <c r="A7" s="2"/>
       <c r="B7" s="2"/>
       <c r="C7" s="2">
         <v>2</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E7" s="2">
         <v>1</v>
       </c>
       <c r="F7" s="2">
+        <v>6</v>
+      </c>
+      <c r="G7" s="2">
         <v>3</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>2001</v>
       </c>
-      <c r="H7" s="2">
+      <c r="I7" s="2">
         <v>20</v>
       </c>
-      <c r="I7" s="2">
-        <v>0</v>
-      </c>
       <c r="J7" s="2">
         <v>0</v>
       </c>
-      <c r="K7" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L7" s="2">
-        <v>100</v>
-      </c>
-      <c r="M7" s="2"/>
+      <c r="K7" s="2">
+        <v>0</v>
+      </c>
+      <c r="L7" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M7" s="2">
+        <v>100</v>
+      </c>
       <c r="N7" s="2"/>
       <c r="O7" s="2"/>
       <c r="P7" s="2"/>
@@ -1372,578 +1478,1201 @@
       <c r="Z7" s="2"/>
       <c r="AA7" s="2"/>
       <c r="AB7" s="2"/>
-    </row>
-    <row r="8" customHeight="1" spans="3:12">
+      <c r="AC7" s="2"/>
+    </row>
+    <row r="8" customHeight="1" spans="3:13">
       <c r="C8" s="2">
         <v>3</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="E8" s="2">
         <v>1</v>
       </c>
       <c r="F8" s="2">
+        <v>6</v>
+      </c>
+      <c r="G8" s="2">
         <v>2</v>
       </c>
-      <c r="G8" s="2">
+      <c r="H8" s="2">
         <v>2001</v>
       </c>
-      <c r="H8" s="2">
+      <c r="I8" s="2">
         <v>30</v>
       </c>
-      <c r="I8" s="2">
-        <v>0</v>
-      </c>
       <c r="J8" s="2">
         <v>0</v>
       </c>
-      <c r="K8" s="2" t="s">
-        <v>15</v>
-      </c>
-      <c r="L8" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="9" customHeight="1" spans="3:12">
+      <c r="K8" s="2">
+        <v>0</v>
+      </c>
+      <c r="L8" s="2" t="s">
+        <v>16</v>
+      </c>
+      <c r="M8" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="9" customHeight="1" spans="3:13">
       <c r="C9" s="2">
         <v>4</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="E9" s="2">
         <v>1</v>
       </c>
       <c r="F9" s="2">
+        <v>6</v>
+      </c>
+      <c r="G9" s="2">
         <v>4</v>
       </c>
-      <c r="G9" s="2">
+      <c r="H9" s="2">
         <v>2002</v>
       </c>
-      <c r="H9" s="2">
-        <v>10</v>
-      </c>
       <c r="I9" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J9" s="2">
         <v>0</v>
       </c>
-      <c r="K9" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L9" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="10" customHeight="1" spans="3:12">
+      <c r="K9" s="2">
+        <v>0</v>
+      </c>
+      <c r="L9" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M9" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="10" customHeight="1" spans="3:13">
       <c r="C10" s="2">
         <v>5</v>
       </c>
       <c r="D10" s="2" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="E10" s="2">
         <v>1</v>
       </c>
       <c r="F10" s="2">
+        <v>6</v>
+      </c>
+      <c r="G10" s="2">
         <v>3</v>
       </c>
-      <c r="G10" s="2">
+      <c r="H10" s="2">
         <v>2002</v>
       </c>
-      <c r="H10" s="2">
+      <c r="I10" s="2">
         <v>20</v>
       </c>
-      <c r="I10" s="2">
-        <v>0</v>
-      </c>
       <c r="J10" s="2">
         <v>0</v>
       </c>
-      <c r="K10" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L10" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="11" customHeight="1" spans="3:12">
+      <c r="K10" s="2">
+        <v>0</v>
+      </c>
+      <c r="L10" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M10" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="11" customHeight="1" spans="3:13">
       <c r="C11" s="2">
         <v>6</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="E11" s="2">
         <v>1</v>
       </c>
       <c r="F11" s="2">
+        <v>6</v>
+      </c>
+      <c r="G11" s="2">
         <v>2</v>
       </c>
-      <c r="G11" s="2">
+      <c r="H11" s="2">
         <v>2002</v>
       </c>
-      <c r="H11" s="2">
+      <c r="I11" s="2">
         <v>30</v>
       </c>
-      <c r="I11" s="2">
-        <v>0</v>
-      </c>
       <c r="J11" s="2">
         <v>0</v>
       </c>
-      <c r="K11" s="2" t="s">
-        <v>19</v>
-      </c>
-      <c r="L11" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="12" customHeight="1" spans="3:12">
+      <c r="K11" s="2">
+        <v>0</v>
+      </c>
+      <c r="L11" s="2" t="s">
+        <v>20</v>
+      </c>
+      <c r="M11" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="12" customHeight="1" spans="3:13">
       <c r="C12" s="2">
         <v>7</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="E12" s="2">
         <v>1</v>
       </c>
       <c r="F12" s="2">
+        <v>6</v>
+      </c>
+      <c r="G12" s="2">
         <v>4</v>
       </c>
-      <c r="G12" s="2">
+      <c r="H12" s="2">
         <v>2003</v>
       </c>
-      <c r="H12" s="2">
-        <v>10</v>
-      </c>
       <c r="I12" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J12" s="2">
         <v>0</v>
       </c>
-      <c r="K12" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L12" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="13" customHeight="1" spans="3:12">
+      <c r="K12" s="2">
+        <v>0</v>
+      </c>
+      <c r="L12" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M12" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="13" customHeight="1" spans="3:13">
       <c r="C13" s="2">
         <v>8</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="E13" s="2">
         <v>1</v>
       </c>
       <c r="F13" s="2">
+        <v>6</v>
+      </c>
+      <c r="G13" s="2">
         <v>3</v>
       </c>
-      <c r="G13" s="2">
+      <c r="H13" s="2">
         <v>2003</v>
       </c>
-      <c r="H13" s="2">
+      <c r="I13" s="2">
         <v>20</v>
       </c>
-      <c r="I13" s="2">
-        <v>0</v>
-      </c>
       <c r="J13" s="2">
         <v>0</v>
       </c>
-      <c r="K13" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L13" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="14" customHeight="1" spans="3:12">
+      <c r="K13" s="2">
+        <v>0</v>
+      </c>
+      <c r="L13" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M13" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="14" customHeight="1" spans="3:13">
       <c r="C14" s="2">
         <v>9</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="E14" s="2">
         <v>1</v>
       </c>
       <c r="F14" s="2">
+        <v>6</v>
+      </c>
+      <c r="G14" s="2">
         <v>2</v>
       </c>
-      <c r="G14" s="2">
+      <c r="H14" s="2">
         <v>2003</v>
       </c>
-      <c r="H14" s="2">
+      <c r="I14" s="2">
         <v>30</v>
       </c>
-      <c r="I14" s="2">
-        <v>0</v>
-      </c>
       <c r="J14" s="2">
         <v>0</v>
       </c>
-      <c r="K14" s="2" t="s">
-        <v>23</v>
-      </c>
-      <c r="L14" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="15" customHeight="1" spans="3:12">
+      <c r="K14" s="2">
+        <v>0</v>
+      </c>
+      <c r="L14" s="2" t="s">
+        <v>24</v>
+      </c>
+      <c r="M14" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="15" customHeight="1" spans="3:13">
       <c r="C15" s="2">
         <v>10</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="E15" s="2">
         <v>1</v>
       </c>
       <c r="F15" s="2">
+        <v>6</v>
+      </c>
+      <c r="G15" s="2">
         <v>4</v>
       </c>
-      <c r="G15" s="2">
+      <c r="H15" s="2">
         <v>12</v>
       </c>
-      <c r="H15" s="2">
-        <v>10</v>
-      </c>
       <c r="I15" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J15" s="2">
         <v>0</v>
       </c>
-      <c r="K15" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L15" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="16" customHeight="1" spans="3:12">
+      <c r="K15" s="2">
+        <v>0</v>
+      </c>
+      <c r="L15" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M15" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="16" customHeight="1" spans="3:13">
       <c r="C16" s="2">
         <v>11</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>28</v>
+        <v>29</v>
       </c>
       <c r="E16" s="2">
         <v>1</v>
       </c>
       <c r="F16" s="2">
+        <v>6</v>
+      </c>
+      <c r="G16" s="2">
         <v>3</v>
       </c>
-      <c r="G16" s="2">
+      <c r="H16" s="2">
         <v>12</v>
       </c>
-      <c r="H16" s="2">
+      <c r="I16" s="2">
         <v>20</v>
       </c>
-      <c r="I16" s="2">
-        <v>0</v>
-      </c>
       <c r="J16" s="2">
         <v>0</v>
       </c>
-      <c r="K16" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L16" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="17" customHeight="1" spans="3:12">
+      <c r="K16" s="2">
+        <v>0</v>
+      </c>
+      <c r="L16" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M16" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="17" customHeight="1" spans="3:13">
       <c r="C17" s="2">
         <v>12</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="E17" s="2">
         <v>1</v>
       </c>
       <c r="F17" s="2">
+        <v>6</v>
+      </c>
+      <c r="G17" s="2">
         <v>2</v>
       </c>
-      <c r="G17" s="2">
+      <c r="H17" s="2">
         <v>12</v>
       </c>
-      <c r="H17" s="2">
+      <c r="I17" s="2">
         <v>30</v>
       </c>
-      <c r="I17" s="2">
-        <v>0</v>
-      </c>
       <c r="J17" s="2">
         <v>0</v>
       </c>
-      <c r="K17" s="2" t="s">
-        <v>27</v>
-      </c>
-      <c r="L17" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="18" customHeight="1" spans="3:12">
+      <c r="K17" s="2">
+        <v>0</v>
+      </c>
+      <c r="L17" s="2" t="s">
+        <v>28</v>
+      </c>
+      <c r="M17" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="18" customHeight="1" spans="3:13">
       <c r="C18" s="2">
         <v>13</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>30</v>
+        <v>31</v>
       </c>
       <c r="E18" s="2">
         <v>1</v>
       </c>
       <c r="F18" s="2">
+        <v>6</v>
+      </c>
+      <c r="G18" s="2">
         <v>4</v>
       </c>
-      <c r="G18" s="2">
+      <c r="H18" s="2">
         <v>13</v>
       </c>
-      <c r="H18" s="2">
-        <v>10</v>
-      </c>
       <c r="I18" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J18" s="2">
         <v>0</v>
       </c>
-      <c r="K18" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L18" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="19" customHeight="1" spans="3:12">
+      <c r="K18" s="2">
+        <v>0</v>
+      </c>
+      <c r="L18" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M18" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="19" customHeight="1" spans="3:13">
       <c r="C19" s="2">
         <v>14</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>32</v>
+        <v>33</v>
       </c>
       <c r="E19" s="2">
         <v>1</v>
       </c>
       <c r="F19" s="2">
+        <v>6</v>
+      </c>
+      <c r="G19" s="2">
         <v>3</v>
       </c>
-      <c r="G19" s="2">
+      <c r="H19" s="2">
         <v>13</v>
       </c>
-      <c r="H19" s="2">
+      <c r="I19" s="2">
         <v>20</v>
       </c>
-      <c r="I19" s="2">
-        <v>0</v>
-      </c>
       <c r="J19" s="2">
         <v>0</v>
       </c>
-      <c r="K19" s="2" t="s">
-        <v>31</v>
-      </c>
-      <c r="L19" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="20" customHeight="1" spans="3:12">
+      <c r="K19" s="2">
+        <v>0</v>
+      </c>
+      <c r="L19" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M19" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="20" customHeight="1" spans="3:13">
       <c r="C20" s="2">
         <v>15</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>33</v>
+        <v>34</v>
       </c>
       <c r="E20" s="2">
         <v>1</v>
       </c>
       <c r="F20" s="2">
+        <v>6</v>
+      </c>
+      <c r="G20" s="2">
         <v>2</v>
       </c>
-      <c r="G20" s="2">
+      <c r="H20" s="2">
         <v>13</v>
       </c>
-      <c r="H20" s="2">
+      <c r="I20" s="2">
         <v>30</v>
       </c>
-      <c r="I20" s="2">
-        <v>0</v>
-      </c>
       <c r="J20" s="2">
         <v>0</v>
       </c>
-      <c r="K20" s="2" t="s">
+      <c r="K20" s="2">
+        <v>0</v>
+      </c>
+      <c r="L20" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="M20" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="22" customHeight="1" spans="3:13">
+      <c r="C22" s="2">
+        <v>101</v>
+      </c>
+      <c r="D22" s="2" t="s">
+        <v>15</v>
+      </c>
+      <c r="E22" s="2">
+        <v>7</v>
+      </c>
+      <c r="F22" s="2">
+        <v>10</v>
+      </c>
+      <c r="G22" s="2">
+        <v>3</v>
+      </c>
+      <c r="H22" s="2">
+        <v>2001</v>
+      </c>
+      <c r="I22" s="2">
+        <v>100</v>
+      </c>
+      <c r="J22" s="2">
+        <v>0</v>
+      </c>
+      <c r="K22" s="2">
+        <v>0</v>
+      </c>
+      <c r="L22" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M22" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="23" customHeight="1" spans="3:13">
+      <c r="C23" s="2">
+        <v>102</v>
+      </c>
+      <c r="D23" s="2" t="s">
+        <v>17</v>
+      </c>
+      <c r="E23" s="2">
+        <v>7</v>
+      </c>
+      <c r="F23" s="2">
+        <v>10</v>
+      </c>
+      <c r="G23" s="2">
+        <v>2</v>
+      </c>
+      <c r="H23" s="2">
+        <v>2001</v>
+      </c>
+      <c r="I23" s="2">
+        <v>200</v>
+      </c>
+      <c r="J23" s="2">
+        <v>0</v>
+      </c>
+      <c r="K23" s="2">
+        <v>0</v>
+      </c>
+      <c r="L23" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M23" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="24" customHeight="1" spans="3:13">
+      <c r="C24" s="2">
+        <v>103</v>
+      </c>
+      <c r="D24" s="2" t="s">
+        <v>18</v>
+      </c>
+      <c r="E24" s="2">
+        <v>7</v>
+      </c>
+      <c r="F24" s="2">
+        <v>10</v>
+      </c>
+      <c r="G24" s="2">
+        <v>1</v>
+      </c>
+      <c r="H24" s="2">
+        <v>2001</v>
+      </c>
+      <c r="I24" s="2">
+        <v>300</v>
+      </c>
+      <c r="J24" s="2">
+        <v>0</v>
+      </c>
+      <c r="K24" s="2">
+        <v>0</v>
+      </c>
+      <c r="L24" s="2" t="s">
+        <v>35</v>
+      </c>
+      <c r="M24" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="25" customHeight="1" spans="3:13">
+      <c r="C25" s="2">
+        <v>104</v>
+      </c>
+      <c r="D25" s="2" t="s">
+        <v>19</v>
+      </c>
+      <c r="E25" s="2">
+        <v>7</v>
+      </c>
+      <c r="F25" s="2">
+        <v>10</v>
+      </c>
+      <c r="G25" s="2">
+        <v>3</v>
+      </c>
+      <c r="H25" s="2">
+        <v>2002</v>
+      </c>
+      <c r="I25" s="2">
+        <v>100</v>
+      </c>
+      <c r="J25" s="2">
+        <v>0</v>
+      </c>
+      <c r="K25" s="2">
+        <v>0</v>
+      </c>
+      <c r="L25" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M25" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="26" customHeight="1" spans="3:13">
+      <c r="C26" s="2">
+        <v>105</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>21</v>
+      </c>
+      <c r="E26" s="2">
+        <v>7</v>
+      </c>
+      <c r="F26" s="2">
+        <v>10</v>
+      </c>
+      <c r="G26" s="2">
+        <v>2</v>
+      </c>
+      <c r="H26" s="2">
+        <v>2002</v>
+      </c>
+      <c r="I26" s="2">
+        <v>200</v>
+      </c>
+      <c r="J26" s="2">
+        <v>0</v>
+      </c>
+      <c r="K26" s="2">
+        <v>0</v>
+      </c>
+      <c r="L26" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M26" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="27" customHeight="1" spans="3:13">
+      <c r="C27" s="2">
+        <v>106</v>
+      </c>
+      <c r="D27" s="2" t="s">
+        <v>22</v>
+      </c>
+      <c r="E27" s="2">
+        <v>7</v>
+      </c>
+      <c r="F27" s="2">
+        <v>10</v>
+      </c>
+      <c r="G27" s="2">
+        <v>1</v>
+      </c>
+      <c r="H27" s="2">
+        <v>2002</v>
+      </c>
+      <c r="I27" s="2">
+        <v>300</v>
+      </c>
+      <c r="J27" s="2">
+        <v>0</v>
+      </c>
+      <c r="K27" s="2">
+        <v>0</v>
+      </c>
+      <c r="L27" s="2" t="s">
+        <v>36</v>
+      </c>
+      <c r="M27" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="28" customHeight="1" spans="3:13">
+      <c r="C28" s="2">
+        <v>107</v>
+      </c>
+      <c r="D28" s="2" t="s">
+        <v>37</v>
+      </c>
+      <c r="E28" s="2">
+        <v>7</v>
+      </c>
+      <c r="F28" s="2">
+        <v>10</v>
+      </c>
+      <c r="G28" s="2">
+        <v>3</v>
+      </c>
+      <c r="H28" s="2">
+        <v>2012</v>
+      </c>
+      <c r="I28" s="2">
+        <v>100</v>
+      </c>
+      <c r="J28" s="2">
+        <v>0</v>
+      </c>
+      <c r="K28" s="2">
+        <v>0</v>
+      </c>
+      <c r="L28" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M28" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="29" customHeight="1" spans="3:13">
+      <c r="C29" s="2">
+        <v>108</v>
+      </c>
+      <c r="D29" s="2" t="s">
+        <v>39</v>
+      </c>
+      <c r="E29" s="2">
+        <v>7</v>
+      </c>
+      <c r="F29" s="2">
+        <v>10</v>
+      </c>
+      <c r="G29" s="2">
+        <v>2</v>
+      </c>
+      <c r="H29" s="2">
+        <v>2012</v>
+      </c>
+      <c r="I29" s="2">
+        <v>200</v>
+      </c>
+      <c r="J29" s="2">
+        <v>0</v>
+      </c>
+      <c r="K29" s="2">
+        <v>0</v>
+      </c>
+      <c r="L29" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M29" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="30" customHeight="1" spans="3:13">
+      <c r="C30" s="2">
+        <v>109</v>
+      </c>
+      <c r="D30" s="2" t="s">
+        <v>40</v>
+      </c>
+      <c r="E30" s="2">
+        <v>7</v>
+      </c>
+      <c r="F30" s="2">
+        <v>10</v>
+      </c>
+      <c r="G30" s="2">
+        <v>1</v>
+      </c>
+      <c r="H30" s="2">
+        <v>2012</v>
+      </c>
+      <c r="I30" s="2">
+        <v>300</v>
+      </c>
+      <c r="J30" s="2">
+        <v>0</v>
+      </c>
+      <c r="K30" s="2">
+        <v>0</v>
+      </c>
+      <c r="L30" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="M30" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="31" customHeight="1" spans="3:13">
+      <c r="C31" s="2">
+        <v>110</v>
+      </c>
+      <c r="D31" s="2" t="s">
+        <v>23</v>
+      </c>
+      <c r="E31" s="2">
+        <v>7</v>
+      </c>
+      <c r="F31" s="2">
+        <v>10</v>
+      </c>
+      <c r="G31" s="2">
+        <v>3</v>
+      </c>
+      <c r="H31" s="2">
+        <v>2003</v>
+      </c>
+      <c r="I31" s="2">
+        <v>100</v>
+      </c>
+      <c r="J31" s="2">
+        <v>0</v>
+      </c>
+      <c r="K31" s="2">
+        <v>0</v>
+      </c>
+      <c r="L31" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M31" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="32" customHeight="1" spans="3:13">
+      <c r="C32" s="2">
+        <v>111</v>
+      </c>
+      <c r="D32" s="2" t="s">
+        <v>25</v>
+      </c>
+      <c r="E32" s="2">
+        <v>7</v>
+      </c>
+      <c r="F32" s="2">
+        <v>10</v>
+      </c>
+      <c r="G32" s="2">
+        <v>2</v>
+      </c>
+      <c r="H32" s="2">
+        <v>2003</v>
+      </c>
+      <c r="I32" s="2">
+        <v>200</v>
+      </c>
+      <c r="J32" s="2">
+        <v>0</v>
+      </c>
+      <c r="K32" s="2">
+        <v>0</v>
+      </c>
+      <c r="L32" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M32" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="33" customHeight="1" spans="3:13">
+      <c r="C33" s="2">
+        <v>112</v>
+      </c>
+      <c r="D33" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="E33" s="2">
+        <v>7</v>
+      </c>
+      <c r="F33" s="2">
+        <v>10</v>
+      </c>
+      <c r="G33" s="2">
+        <v>1</v>
+      </c>
+      <c r="H33" s="2">
+        <v>2003</v>
+      </c>
+      <c r="I33" s="2">
+        <v>300</v>
+      </c>
+      <c r="J33" s="2">
+        <v>0</v>
+      </c>
+      <c r="K33" s="2">
+        <v>0</v>
+      </c>
+      <c r="L33" s="2" t="s">
+        <v>41</v>
+      </c>
+      <c r="M33" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="34" customHeight="1" spans="3:13">
+      <c r="C34" s="2">
+        <v>113</v>
+      </c>
+      <c r="D34" s="2" t="s">
+        <v>27</v>
+      </c>
+      <c r="E34" s="2">
+        <v>7</v>
+      </c>
+      <c r="F34" s="2">
+        <v>10</v>
+      </c>
+      <c r="G34" s="2">
+        <v>3</v>
+      </c>
+      <c r="H34" s="2">
+        <v>2011</v>
+      </c>
+      <c r="I34" s="2">
+        <v>100</v>
+      </c>
+      <c r="J34" s="2">
+        <v>0</v>
+      </c>
+      <c r="K34" s="2">
+        <v>0</v>
+      </c>
+      <c r="L34" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M34" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="35" customHeight="1" spans="3:13">
+      <c r="C35" s="2">
+        <v>114</v>
+      </c>
+      <c r="D35" s="2" t="s">
+        <v>29</v>
+      </c>
+      <c r="E35" s="2">
+        <v>7</v>
+      </c>
+      <c r="F35" s="2">
+        <v>10</v>
+      </c>
+      <c r="G35" s="2">
+        <v>2</v>
+      </c>
+      <c r="H35" s="2">
+        <v>2011</v>
+      </c>
+      <c r="I35" s="2">
+        <v>200</v>
+      </c>
+      <c r="J35" s="2">
+        <v>0</v>
+      </c>
+      <c r="K35" s="2">
+        <v>0</v>
+      </c>
+      <c r="L35" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M35" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="36" customHeight="1" spans="3:13">
+      <c r="C36" s="2">
+        <v>115</v>
+      </c>
+      <c r="D36" s="2" t="s">
+        <v>30</v>
+      </c>
+      <c r="E36" s="2">
+        <v>7</v>
+      </c>
+      <c r="F36" s="2">
+        <v>10</v>
+      </c>
+      <c r="G36" s="2">
+        <v>1</v>
+      </c>
+      <c r="H36" s="2">
+        <v>2011</v>
+      </c>
+      <c r="I36" s="2">
+        <v>300</v>
+      </c>
+      <c r="J36" s="2">
+        <v>0</v>
+      </c>
+      <c r="K36" s="2">
+        <v>0</v>
+      </c>
+      <c r="L36" s="2" t="s">
+        <v>42</v>
+      </c>
+      <c r="M36" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="37" customHeight="1" spans="3:13">
+      <c r="C37" s="2">
+        <v>116</v>
+      </c>
+      <c r="D37" s="2" t="s">
+        <v>43</v>
+      </c>
+      <c r="E37" s="2">
+        <v>7</v>
+      </c>
+      <c r="F37" s="2">
+        <v>10</v>
+      </c>
+      <c r="G37" s="2">
+        <v>3</v>
+      </c>
+      <c r="H37" s="2">
+        <v>32</v>
+      </c>
+      <c r="I37" s="2">
+        <v>3</v>
+      </c>
+      <c r="J37" s="2">
+        <v>0</v>
+      </c>
+      <c r="K37" s="2">
+        <v>0</v>
+      </c>
+      <c r="L37" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M37" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="38" customHeight="1" spans="3:13">
+      <c r="C38" s="2">
+        <v>117</v>
+      </c>
+      <c r="D38" s="2" t="s">
+        <v>45</v>
+      </c>
+      <c r="E38" s="2">
+        <v>7</v>
+      </c>
+      <c r="F38" s="2">
+        <v>10</v>
+      </c>
+      <c r="G38" s="2">
+        <v>2</v>
+      </c>
+      <c r="H38" s="2">
+        <v>32</v>
+      </c>
+      <c r="I38" s="2">
+        <v>7</v>
+      </c>
+      <c r="J38" s="2">
+        <v>0</v>
+      </c>
+      <c r="K38" s="2">
+        <v>0</v>
+      </c>
+      <c r="L38" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M38" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="39" customHeight="1" spans="3:13">
+      <c r="C39" s="2">
+        <v>118</v>
+      </c>
+      <c r="D39" s="2" t="s">
+        <v>46</v>
+      </c>
+      <c r="E39" s="2">
+        <v>7</v>
+      </c>
+      <c r="F39" s="2">
+        <v>10</v>
+      </c>
+      <c r="G39" s="2">
+        <v>1</v>
+      </c>
+      <c r="H39" s="2">
+        <v>32</v>
+      </c>
+      <c r="I39" s="2">
+        <v>10</v>
+      </c>
+      <c r="J39" s="2">
+        <v>0</v>
+      </c>
+      <c r="K39" s="2">
+        <v>0</v>
+      </c>
+      <c r="L39" s="2" t="s">
+        <v>44</v>
+      </c>
+      <c r="M39" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="40" customHeight="1" spans="3:13">
+      <c r="C40" s="2">
+        <v>119</v>
+      </c>
+      <c r="D40" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="E40" s="2">
+        <v>7</v>
+      </c>
+      <c r="F40" s="2">
+        <v>10</v>
+      </c>
+      <c r="G40" s="2">
+        <v>3</v>
+      </c>
+      <c r="H40" s="2">
         <v>31</v>
       </c>
-      <c r="L20" s="2">
-        <v>100</v>
-      </c>
-    </row>
-    <row r="22" customHeight="1" spans="1:12">
-      <c r="A22" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B22" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C22" s="2">
-        <v>1000</v>
-      </c>
-      <c r="D22" s="2" t="s">
-        <v>34</v>
-      </c>
-      <c r="E22" s="2">
+      <c r="I40" s="2">
+        <v>5</v>
+      </c>
+      <c r="J40" s="2">
+        <v>0</v>
+      </c>
+      <c r="K40" s="2">
+        <v>0</v>
+      </c>
+      <c r="L40" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M40" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="41" customHeight="1" spans="3:13">
+      <c r="C41" s="2">
+        <v>120</v>
+      </c>
+      <c r="D41" s="2" t="s">
+        <v>49</v>
+      </c>
+      <c r="E41" s="2">
+        <v>7</v>
+      </c>
+      <c r="F41" s="2">
+        <v>10</v>
+      </c>
+      <c r="G41" s="2">
         <v>2</v>
       </c>
-      <c r="F22" s="2">
+      <c r="H41" s="2">
+        <v>31</v>
+      </c>
+      <c r="I41" s="2">
+        <v>10</v>
+      </c>
+      <c r="J41" s="2">
+        <v>0</v>
+      </c>
+      <c r="K41" s="2">
+        <v>0</v>
+      </c>
+      <c r="L41" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M41" s="2">
+        <v>100</v>
+      </c>
+    </row>
+    <row r="42" customHeight="1" spans="3:13">
+      <c r="C42" s="2">
+        <v>121</v>
+      </c>
+      <c r="D42" s="2" t="s">
+        <v>50</v>
+      </c>
+      <c r="E42" s="2">
+        <v>7</v>
+      </c>
+      <c r="F42" s="2">
+        <v>10</v>
+      </c>
+      <c r="G42" s="2">
         <v>1</v>
       </c>
-      <c r="G22" s="2">
-        <v>0</v>
-      </c>
-      <c r="H22" s="2">
-        <v>0</v>
-      </c>
-      <c r="I22" s="2">
-        <v>0</v>
-      </c>
-      <c r="J22" s="2">
-        <v>1001</v>
-      </c>
-      <c r="K22" s="2" t="s">
-        <v>35</v>
-      </c>
-      <c r="L22" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="23" customHeight="1" spans="1:12">
-      <c r="A23" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B23" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C23" s="2">
-        <v>1001</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>36</v>
-      </c>
-      <c r="E23" s="2">
-        <v>2</v>
-      </c>
-      <c r="F23" s="2">
-        <v>1</v>
-      </c>
-      <c r="G23" s="2">
-        <v>0</v>
-      </c>
-      <c r="H23" s="2">
-        <v>0</v>
-      </c>
-      <c r="I23" s="2">
-        <v>0</v>
-      </c>
-      <c r="J23" s="2">
-        <v>1002</v>
-      </c>
-      <c r="K23" s="2" t="s">
-        <v>37</v>
-      </c>
-      <c r="L23" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="25" customHeight="1" spans="1:12">
-      <c r="A25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B25" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C25" s="2">
-        <v>2000</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>38</v>
-      </c>
-      <c r="E25" s="2">
-        <v>3</v>
-      </c>
-      <c r="F25" s="2">
-        <v>1</v>
-      </c>
-      <c r="G25" s="2">
-        <v>0</v>
-      </c>
-      <c r="H25" s="2">
-        <v>0</v>
-      </c>
-      <c r="I25" s="2">
-        <v>2010</v>
-      </c>
-      <c r="J25" s="2">
-        <v>0</v>
-      </c>
-      <c r="K25" s="4" t="s">
-        <v>39</v>
-      </c>
-      <c r="L25" s="2">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="26" customHeight="1" spans="1:12">
-      <c r="A26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="B26" s="2" t="s">
-        <v>0</v>
-      </c>
-      <c r="C26" s="2">
-        <v>2001</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>40</v>
-      </c>
-      <c r="E26" s="2">
-        <v>3</v>
-      </c>
-      <c r="F26" s="2">
-        <v>1</v>
-      </c>
-      <c r="G26" s="2">
-        <v>0</v>
-      </c>
-      <c r="H26" s="2">
-        <v>0</v>
-      </c>
-      <c r="I26" s="2">
-        <v>21009</v>
-      </c>
-      <c r="J26" s="2">
-        <v>0</v>
-      </c>
-      <c r="K26" s="2" t="s">
-        <v>41</v>
-      </c>
-      <c r="L26" s="2">
-        <v>10</v>
+      <c r="H42" s="2">
+        <v>31</v>
+      </c>
+      <c r="I42" s="2">
+        <v>15</v>
+      </c>
+      <c r="J42" s="2">
+        <v>0</v>
+      </c>
+      <c r="K42" s="2">
+        <v>0</v>
+      </c>
+      <c r="L42" s="2" t="s">
+        <v>48</v>
+      </c>
+      <c r="M42" s="2">
+        <v>100</v>
       </c>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:H3 K3:M3 G4:H4 L4:M4 G5:H5 L5:M5 K4:K5 C3:D5 I3:J5 E4:F5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:I3 F4:I4 F5:I5 E4:E5 C3:D5 J3:N5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>

--- a/Excel/DefendBuffConfig.xlsx
+++ b/Excel/DefendBuffConfig.xlsx
@@ -469,12 +469,12 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
     </font>
     <font>
+      <b/>
       <sz val="9"/>
       <name val="宋体"/>
       <charset val="134"/>
@@ -1279,12 +1279,12 @@
     <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="2" customHeight="1" spans="14:14">
+    <row r="2" customHeight="1" spans="1:29">
       <c r="N2" s="2" t="s">
         <v>0</v>
       </c>
     </row>
-    <row r="3" customHeight="1" spans="3:14">
+    <row r="3" customHeight="1" spans="1:29">
       <c r="C3" s="3" t="s">
         <v>1</v>
       </c>
@@ -1320,7 +1320,7 @@
       </c>
       <c r="N3" s="3"/>
     </row>
-    <row r="4" customHeight="1" spans="3:14">
+    <row r="4" customHeight="1" spans="1:29">
       <c r="C4" s="3" t="s">
         <v>12</v>
       </c>
@@ -1356,7 +1356,7 @@
       </c>
       <c r="N4" s="3"/>
     </row>
-    <row r="5" customHeight="1" spans="3:14">
+    <row r="5" customHeight="1" spans="1:29">
       <c r="C5" s="3" t="s">
         <v>13</v>
       </c>
@@ -1392,7 +1392,7 @@
       </c>
       <c r="N5" s="3"/>
     </row>
-    <row r="6" customHeight="1" spans="3:13">
+    <row r="6" customHeight="1" spans="1:29">
       <c r="C6" s="2">
         <v>1</v>
       </c>
@@ -1480,7 +1480,7 @@
       <c r="AB7" s="2"/>
       <c r="AC7" s="2"/>
     </row>
-    <row r="8" customHeight="1" spans="3:13">
+    <row r="8" customHeight="1" spans="1:29">
       <c r="C8" s="2">
         <v>3</v>
       </c>
@@ -1515,7 +1515,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="9" customHeight="1" spans="3:13">
+    <row r="9" customHeight="1" spans="1:29">
       <c r="C9" s="2">
         <v>4</v>
       </c>
@@ -1550,7 +1550,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="10" customHeight="1" spans="3:13">
+    <row r="10" customHeight="1" spans="1:29">
       <c r="C10" s="2">
         <v>5</v>
       </c>
@@ -1585,7 +1585,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="11" customHeight="1" spans="3:13">
+    <row r="11" customHeight="1" spans="1:29">
       <c r="C11" s="2">
         <v>6</v>
       </c>
@@ -1620,7 +1620,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="12" customHeight="1" spans="3:13">
+    <row r="12" customHeight="1" spans="1:29">
       <c r="C12" s="2">
         <v>7</v>
       </c>
@@ -1655,7 +1655,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="13" customHeight="1" spans="3:13">
+    <row r="13" customHeight="1" spans="1:29">
       <c r="C13" s="2">
         <v>8</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="14" customHeight="1" spans="3:13">
+    <row r="14" customHeight="1" spans="1:29">
       <c r="C14" s="2">
         <v>9</v>
       </c>
@@ -1725,7 +1725,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="15" customHeight="1" spans="3:13">
+    <row r="15" customHeight="1" spans="1:29">
       <c r="C15" s="2">
         <v>10</v>
       </c>
@@ -1760,7 +1760,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="16" customHeight="1" spans="3:13">
+    <row r="16" customHeight="1" spans="1:29">
       <c r="C16" s="2">
         <v>11</v>
       </c>
@@ -1946,7 +1946,7 @@
         <v>7</v>
       </c>
       <c r="F22" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G22" s="2">
         <v>3</v>
@@ -1981,7 +1981,7 @@
         <v>7</v>
       </c>
       <c r="F23" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G23" s="2">
         <v>2</v>
@@ -2016,7 +2016,7 @@
         <v>7</v>
       </c>
       <c r="F24" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G24" s="2">
         <v>1</v>
@@ -2051,7 +2051,7 @@
         <v>7</v>
       </c>
       <c r="F25" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G25" s="2">
         <v>3</v>
@@ -2086,7 +2086,7 @@
         <v>7</v>
       </c>
       <c r="F26" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G26" s="2">
         <v>2</v>
@@ -2121,7 +2121,7 @@
         <v>7</v>
       </c>
       <c r="F27" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G27" s="2">
         <v>1</v>
@@ -2156,7 +2156,7 @@
         <v>7</v>
       </c>
       <c r="F28" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G28" s="2">
         <v>3</v>
@@ -2191,7 +2191,7 @@
         <v>7</v>
       </c>
       <c r="F29" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G29" s="2">
         <v>2</v>
@@ -2226,7 +2226,7 @@
         <v>7</v>
       </c>
       <c r="F30" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G30" s="2">
         <v>1</v>
@@ -2261,7 +2261,7 @@
         <v>7</v>
       </c>
       <c r="F31" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G31" s="2">
         <v>3</v>
@@ -2296,7 +2296,7 @@
         <v>7</v>
       </c>
       <c r="F32" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G32" s="2">
         <v>2</v>
@@ -2331,7 +2331,7 @@
         <v>7</v>
       </c>
       <c r="F33" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G33" s="2">
         <v>1</v>
@@ -2366,7 +2366,7 @@
         <v>7</v>
       </c>
       <c r="F34" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G34" s="2">
         <v>3</v>
@@ -2401,7 +2401,7 @@
         <v>7</v>
       </c>
       <c r="F35" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G35" s="2">
         <v>2</v>
@@ -2436,7 +2436,7 @@
         <v>7</v>
       </c>
       <c r="F36" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G36" s="2">
         <v>1</v>
@@ -2471,7 +2471,7 @@
         <v>7</v>
       </c>
       <c r="F37" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G37" s="2">
         <v>3</v>
@@ -2506,7 +2506,7 @@
         <v>7</v>
       </c>
       <c r="F38" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G38" s="2">
         <v>2</v>
@@ -2541,7 +2541,7 @@
         <v>7</v>
       </c>
       <c r="F39" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G39" s="2">
         <v>1</v>
@@ -2576,7 +2576,7 @@
         <v>7</v>
       </c>
       <c r="F40" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G40" s="2">
         <v>3</v>
@@ -2611,7 +2611,7 @@
         <v>7</v>
       </c>
       <c r="F41" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G41" s="2">
         <v>2</v>
@@ -2646,7 +2646,7 @@
         <v>7</v>
       </c>
       <c r="F42" s="2">
-        <v>10</v>
+        <v>99</v>
       </c>
       <c r="G42" s="2">
         <v>1</v>
@@ -2672,7 +2672,7 @@
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="E3:I3 F4:I4 F5:I5 E4:E5 C3:D5 J3:N5" errorStyle="warning">
+    <dataValidation type="custom" allowBlank="1" showErrorMessage="1" errorTitle="拒绝重复输入" error="当前输入的内容，与本区域的其他单元格内容重复。" sqref="C3:N5" errorStyle="warning">
       <formula1>COUNTIF($C:$C,C3)&lt;2</formula1>
     </dataValidation>
   </dataValidations>
